--- a/Human_check.xlsx
+++ b/Human_check.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stefangaman/Documents/ASE/Papers/FinderLLM_Evaluation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489A5E6C-D166-134F-8761-6CE6DD506DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAD728E-F427-3346-88EF-D80654FC582D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="1" xr2:uid="{9BE3AEB7-A3A8-094A-8D88-0AC83DCBDEC2}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20040" activeTab="1" xr2:uid="{9BE3AEB7-A3A8-094A-8D88-0AC83DCBDEC2}"/>
   </bookViews>
   <sheets>
     <sheet name="Visual" sheetId="1" r:id="rId1"/>
@@ -168,16 +168,16 @@
     <t>Y axis</t>
   </si>
   <si>
-    <t xml:space="preserve">The capabilities of LLMs to read and understand financial charts have been discussed over the years. Different researchers brought different results and solutions based on both the LLM model and the moment of time. 
-During our experiments we found out that there are some aspects to be considered when using LLMs to interpret financial charts. One of the msot important aspect is the complexity of it, which highly influences the performance of the results. The higher the complexity of a chart, the lower of the performance of the LLM into udnerstanding it.
-The second one is visual quality of it translated into bigger size labels (text), thicker lines and cleaner picture. Definetly, the charts with a better visual got higher perfoamnce. </t>
+    <t>The ability of large language models (LLMs) to read and interpret financial charts has been widely discussed in recent years. Existing research has reported varied results, depending on the specific LLM used and the period in which the evaluation was conducted.
+Our experiments indicate that several factors should be considered when using LLMs to interpret financial charts. One of the most important factors is chart complexity, which strongly affects performance. As chart complexity increases, the LLM’s ability to correctly interpret the information presented tends to decline.
+A second important factor is visual quality. Charts with larger and more readable labels, thicker lines, and a cleaner overall design generally lead to better performance. In our experiments, LLMs achieved higher accuracy when analysing visually clear and well-structured charts.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -197,12 +197,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -298,11 +292,11 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -730,7 +724,7 @@
       <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -743,7 +737,7 @@
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
+      <c r="A5" s="13"/>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
@@ -754,7 +748,7 @@
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="12"/>
+      <c r="A6" s="13"/>
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
@@ -765,7 +759,7 @@
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -778,7 +772,7 @@
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
@@ -789,7 +783,7 @@
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
+      <c r="A9" s="13"/>
       <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
@@ -800,7 +794,7 @@
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
@@ -811,7 +805,7 @@
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
+      <c r="A11" s="13"/>
       <c r="B11" s="1" t="s">
         <v>14</v>
       </c>
@@ -822,7 +816,7 @@
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
+      <c r="A12" s="13"/>
       <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
@@ -934,7 +928,7 @@
       <c r="N3" s="10"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -954,7 +948,7 @@
       <c r="N4" s="10"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
+      <c r="A5" s="13"/>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,7 +966,7 @@
       <c r="N5" s="10"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A6" s="12"/>
+      <c r="A6" s="13"/>
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
@@ -990,7 +984,7 @@
       <c r="N6" s="10"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -1011,7 +1005,7 @@
       <c r="O7" s="10"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
@@ -1030,7 +1024,7 @@
       <c r="O8" s="10"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
+      <c r="A9" s="13"/>
       <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
@@ -1049,7 +1043,7 @@
       <c r="O9" s="10"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
@@ -1068,7 +1062,7 @@
       <c r="O10" s="10"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
+      <c r="A11" s="13"/>
       <c r="B11" s="1" t="s">
         <v>14</v>
       </c>
@@ -1087,7 +1081,7 @@
       <c r="O11" s="10"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
+      <c r="A12" s="13"/>
       <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
@@ -1105,8 +1099,8 @@
       <c r="N12" s="10"/>
       <c r="O12" s="10"/>
     </row>
-    <row r="18" spans="2:2" ht="340" x14ac:dyDescent="0.2">
-      <c r="B18" s="13" t="s">
+    <row r="18" spans="2:2" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="B18" s="12" t="s">
         <v>21</v>
       </c>
     </row>
